--- a/docs/examples/demo_training_log.xlsx
+++ b/docs/examples/demo_training_log.xlsx
@@ -15016,7 +15016,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-04-18T00:37:27</t>
+          <t>2026-04-18T00:49:27</t>
         </is>
       </c>
     </row>
